--- a/xlsx/carteira_mensal/Set_2026.xlsx
+++ b/xlsx/carteira_mensal/Set_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="113">
   <si>
     <t>Acompanhamento de Carteira</t>
   </si>
@@ -75,24 +75,24 @@
     <t>Data de Criação do Projeto</t>
   </si>
   <si>
+    <t>/  /     até   /  /</t>
+  </si>
+  <si>
+    <t>Data de Criação do Orçamento</t>
+  </si>
+  <si>
+    <t>/  /     00:00 até   /  /     00:00</t>
+  </si>
+  <si>
+    <t>Data de Criação do Contrato</t>
+  </si>
+  <si>
+    <t>Data de Assinatura do Contrato</t>
+  </si>
+  <si>
     <t>01/09/2026 até 30/09/2026</t>
   </si>
   <si>
-    <t>Data de Criação do Orçamento</t>
-  </si>
-  <si>
-    <t>/  /     00:00 até   /  /     00:00</t>
-  </si>
-  <si>
-    <t>Data de Criação do Contrato</t>
-  </si>
-  <si>
-    <t>/  /     até   /  /</t>
-  </si>
-  <si>
-    <t>Data de Assinatura do Contrato</t>
-  </si>
-  <si>
     <t>Data de Criação do Cliente</t>
   </si>
   <si>
@@ -153,33 +153,87 @@
     <t>Contrato</t>
   </si>
   <si>
+    <t>Tadeu Toledo Mathias</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>20/01/26</t>
+  </si>
+  <si>
+    <t>ROSANGELA PACHECO</t>
+  </si>
+  <si>
+    <t>Orçamento 2</t>
+  </si>
+  <si>
+    <t>08/09/26</t>
+  </si>
+  <si>
+    <t>FABIO FERREIRA DAMASIO</t>
+  </si>
+  <si>
+    <t>Porta</t>
+  </si>
+  <si>
+    <t>20/08/26</t>
+  </si>
+  <si>
+    <t>Victor Costa</t>
+  </si>
+  <si>
+    <t>DORMITÓRIO E HOME OFFICE</t>
+  </si>
+  <si>
+    <t>09/09/26</t>
+  </si>
+  <si>
+    <t>Alexandre Augusto Silva Machado</t>
+  </si>
+  <si>
+    <t>Já é Cliente</t>
+  </si>
+  <si>
+    <t>21/08/26</t>
+  </si>
+  <si>
+    <t>ERIC SERPA</t>
+  </si>
+  <si>
+    <t>Orçamento 1</t>
+  </si>
+  <si>
+    <t>12/09/26</t>
+  </si>
+  <si>
+    <t>Enno Albert Winter</t>
+  </si>
+  <si>
+    <t>25/08/26</t>
+  </si>
+  <si>
+    <t>21/09/26</t>
+  </si>
+  <si>
+    <t>DANIELA IDA MENEGATTI MILANO</t>
+  </si>
+  <si>
+    <t>26/08/26</t>
+  </si>
+  <si>
+    <t>BIANCA RODRIGUES</t>
+  </si>
+  <si>
     <t>VERA LUCIA NOGUEIRA FRANCO MOYSES</t>
   </si>
   <si>
-    <t>Porta</t>
-  </si>
-  <si>
     <t>04/09/26</t>
   </si>
   <si>
-    <t>Victor Costa</t>
-  </si>
-  <si>
-    <t>Orçamento 1</t>
-  </si>
-  <si>
-    <t>08/09/26</t>
-  </si>
-  <si>
     <t>BRUNO RODRIGUES VASCONCELLOS</t>
   </si>
   <si>
-    <t>Já é Cliente</t>
-  </si>
-  <si>
-    <t>BIANCA RODRIGUES</t>
-  </si>
-  <si>
     <t>Tatiana Wagner Kissmann</t>
   </si>
   <si>
@@ -201,15 +255,6 @@
     <t>22/09/26</t>
   </si>
   <si>
-    <t>Enno Albert Winter</t>
-  </si>
-  <si>
-    <t>21/09/26</t>
-  </si>
-  <si>
-    <t>ROSANGELA PACHECO</t>
-  </si>
-  <si>
     <t>Guilherme Nunes araujo</t>
   </si>
   <si>
@@ -255,22 +300,16 @@
     <t>28/09/26</t>
   </si>
   <si>
-    <t>ERIC SERPA</t>
-  </si>
-  <si>
     <t>29/09/26</t>
   </si>
   <si>
     <t>Márcia Elias Abucham</t>
   </si>
   <si>
-    <t>Google</t>
-  </si>
-  <si>
     <t>Quantidade de Projetos</t>
   </si>
   <si>
-    <t>12</t>
+    <t>17</t>
   </si>
   <si>
     <t>Quantidade de Orçamentos</t>
@@ -279,40 +318,40 @@
     <t>Pontuação Total</t>
   </si>
   <si>
-    <t>1.95</t>
+    <t>1.94</t>
   </si>
   <si>
     <t>Valor Total Bruto</t>
   </si>
   <si>
-    <t>365.744,21</t>
-  </si>
-  <si>
-    <t>257.815,16</t>
+    <t>532.499,84</t>
+  </si>
+  <si>
+    <t>374.872,66</t>
   </si>
   <si>
     <t>Valor Total Líquido</t>
   </si>
   <si>
-    <t>241.979,55</t>
+    <t>351.257,28</t>
   </si>
   <si>
     <t>Total Líquido sem o Per</t>
   </si>
   <si>
-    <t>240.341,88</t>
+    <t>349.619,61</t>
   </si>
   <si>
     <t>Total Diferença Financeira</t>
   </si>
   <si>
-    <t>15.835,61</t>
+    <t>23.615,38</t>
   </si>
   <si>
     <t>Total Adicional dos Ambientes</t>
   </si>
   <si>
-    <t>12.705,47</t>
+    <t>17.636,32</t>
   </si>
 </sst>
 </file>
@@ -381,7 +420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:O53"/>
+  <dimension ref="A2:O58"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="59.140625" customWidth="true" bestFit="true"/>
@@ -509,15 +548,15 @@
         <v>23</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -525,7 +564,7 @@
         <v>26</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -533,7 +572,7 @@
         <v>27</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -639,7 +678,7 @@
         <v>47</v>
       </c>
       <c r="C31" t="n">
-        <v>987.0</v>
+        <v>561.0</v>
       </c>
       <c r="D31" t="s">
         <v>48</v>
@@ -648,7 +687,7 @@
         <v>49</v>
       </c>
       <c r="F31" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G31" t="s">
         <v>50</v>
@@ -657,22 +696,22 @@
         <v>51</v>
       </c>
       <c r="I31" t="n">
-        <v>300.0</v>
+        <v>2932.99</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0</v>
+        <v>143.49</v>
       </c>
       <c r="K31" t="n">
-        <v>300.0</v>
+        <v>2789.5</v>
       </c>
       <c r="L31" t="n">
-        <v>300.0</v>
+        <v>2789.5</v>
       </c>
       <c r="M31" t="n">
-        <v>2.02</v>
+        <v>2.64</v>
       </c>
       <c r="N31" t="n">
-        <v>98701.0</v>
+        <v>56102.0</v>
       </c>
       <c r="O31" t="s">
         <v>51</v>
@@ -686,87 +725,87 @@
         <v>53</v>
       </c>
       <c r="C32" t="n">
-        <v>994.0</v>
+        <v>954.0</v>
       </c>
       <c r="D32" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F32" t="n">
         <v>1.0</v>
       </c>
       <c r="G32" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H32" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="I32" t="n">
-        <v>300.0</v>
+        <v>46800.0</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0</v>
+        <v>2546.64</v>
       </c>
       <c r="K32" t="n">
-        <v>300.0</v>
+        <v>44253.36</v>
       </c>
       <c r="L32" t="n">
-        <v>300.0</v>
+        <v>44253.36</v>
       </c>
       <c r="M32" t="n">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="N32" t="n">
-        <v>99401.0</v>
+        <v>95401.0</v>
       </c>
       <c r="O32" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B33" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="C33" t="n">
-        <v>1003.0</v>
+        <v>957.0</v>
       </c>
       <c r="D33" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E33" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F33" t="n">
         <v>1.0</v>
       </c>
       <c r="G33" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="H33" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="I33" t="n">
-        <v>29900.0</v>
+        <v>10107.67</v>
       </c>
       <c r="J33" t="n">
-        <v>3178.28</v>
+        <v>874.22</v>
       </c>
       <c r="K33" t="n">
-        <v>26721.72</v>
+        <v>9233.45</v>
       </c>
       <c r="L33" t="n">
-        <v>26721.72</v>
+        <v>9233.45</v>
       </c>
       <c r="M33" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="N33" t="n">
-        <v>100301.0</v>
+        <v>95701.0</v>
       </c>
       <c r="O33" t="s">
         <v>57</v>
@@ -774,93 +813,93 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B34" t="s">
         <v>59</v>
       </c>
       <c r="C34" t="n">
-        <v>1005.0</v>
+        <v>966.0</v>
       </c>
       <c r="D34" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E34" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="F34" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G34" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="H34" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="I34" t="n">
-        <v>22000.0</v>
+        <v>41216.84</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0</v>
+        <v>3415.17</v>
       </c>
       <c r="K34" t="n">
-        <v>22000.0</v>
+        <v>37801.67</v>
       </c>
       <c r="L34" t="n">
-        <v>22000.0</v>
+        <v>37801.67</v>
       </c>
       <c r="M34" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="N34" t="n">
-        <v>100501.0</v>
+        <v>96601.0</v>
       </c>
       <c r="O34" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
+        <v>67</v>
+      </c>
+      <c r="B35" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" t="n">
+        <v>969.0</v>
+      </c>
+      <c r="D35" t="s">
+        <v>68</v>
+      </c>
+      <c r="E35" t="s">
+        <v>69</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G35" t="s">
         <v>62</v>
-      </c>
-      <c r="B35" t="s">
-        <v>53</v>
-      </c>
-      <c r="C35" t="n">
-        <v>1014.0</v>
-      </c>
-      <c r="D35" t="s">
-        <v>63</v>
-      </c>
-      <c r="E35" t="s">
-        <v>64</v>
-      </c>
-      <c r="F35" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G35" t="s">
-        <v>50</v>
       </c>
       <c r="H35" t="s">
         <v>63</v>
       </c>
       <c r="I35" t="n">
-        <v>32583.16</v>
+        <v>16000.0</v>
       </c>
       <c r="J35" t="n">
-        <v>2699.79</v>
+        <v>800.25</v>
       </c>
       <c r="K35" t="n">
-        <v>29883.37</v>
+        <v>15199.75</v>
       </c>
       <c r="L35" t="n">
-        <v>29883.37</v>
+        <v>15199.75</v>
       </c>
       <c r="M35" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="N35" t="n">
-        <v>101401.0</v>
+        <v>96901.0</v>
       </c>
       <c r="O35" t="s">
         <v>63</v>
@@ -868,234 +907,234 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B36" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C36" t="n">
-        <v>1012.0</v>
+        <v>987.0</v>
       </c>
       <c r="D36" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E36" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F36" t="n">
         <v>1.0</v>
       </c>
       <c r="G36" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="H36" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="I36" t="n">
-        <v>15000.0</v>
+        <v>300.0</v>
       </c>
       <c r="J36" t="n">
-        <v>360.92</v>
+        <v>0.0</v>
       </c>
       <c r="K36" t="n">
-        <v>14639.08</v>
+        <v>300.0</v>
       </c>
       <c r="L36" t="n">
-        <v>14639.08</v>
+        <v>300.0</v>
       </c>
       <c r="M36" t="n">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="N36" t="n">
-        <v>101201.0</v>
+        <v>98701.0</v>
       </c>
       <c r="O36" t="s">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="B37" t="s">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="C37" t="n">
-        <v>1011.0</v>
+        <v>994.0</v>
       </c>
       <c r="D37" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="E37" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F37" t="n">
         <v>1.0</v>
       </c>
       <c r="G37" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="H37" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="I37" t="n">
-        <v>60000.0</v>
+        <v>300.0</v>
       </c>
       <c r="J37" t="n">
-        <v>2201.56</v>
+        <v>0.0</v>
       </c>
       <c r="K37" t="n">
-        <v>57798.44</v>
+        <v>300.0</v>
       </c>
       <c r="L37" t="n">
-        <v>56160.77</v>
+        <v>300.0</v>
       </c>
       <c r="M37" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="N37" t="n">
-        <v>101101.0</v>
+        <v>99401.0</v>
       </c>
       <c r="O37" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B38" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C38" t="n">
-        <v>1017.0</v>
+        <v>1003.0</v>
       </c>
       <c r="D38" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="E38" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="F38" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G38" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H38" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I38" t="n">
-        <v>300.0</v>
+        <v>29900.0</v>
       </c>
       <c r="J38" t="n">
-        <v>0.0</v>
+        <v>3178.28</v>
       </c>
       <c r="K38" t="n">
-        <v>300.0</v>
+        <v>26721.72</v>
       </c>
       <c r="L38" t="n">
-        <v>300.0</v>
+        <v>26721.72</v>
       </c>
       <c r="M38" t="n">
-        <v>3.0</v>
+        <v>2.2</v>
       </c>
       <c r="N38" t="n">
-        <v>101701.0</v>
+        <v>100301.0</v>
       </c>
       <c r="O38" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B39" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="C39" t="n">
-        <v>1021.0</v>
+        <v>1005.0</v>
       </c>
       <c r="D39" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E39" t="s">
-        <v>54</v>
+        <v>69</v>
       </c>
       <c r="F39" t="n">
         <v>1.0</v>
       </c>
       <c r="G39" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="H39" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
       <c r="I39" t="n">
-        <v>25000.0</v>
+        <v>22000.0</v>
       </c>
       <c r="J39" t="n">
-        <v>917.32</v>
+        <v>0.0</v>
       </c>
       <c r="K39" t="n">
-        <v>24082.68</v>
+        <v>22000.0</v>
       </c>
       <c r="L39" t="n">
-        <v>24082.68</v>
+        <v>22000.0</v>
       </c>
       <c r="M39" t="n">
         <v>1.9</v>
       </c>
       <c r="N39" t="n">
-        <v>102101.0</v>
+        <v>100501.0</v>
       </c>
       <c r="O39" t="s">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="B40" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="C40" t="n">
-        <v>1018.0</v>
+        <v>1014.0</v>
       </c>
       <c r="D40" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="E40" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="F40" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G40" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="H40" t="s">
         <v>66</v>
       </c>
       <c r="I40" t="n">
-        <v>24432.0</v>
+        <v>32583.16</v>
       </c>
       <c r="J40" t="n">
-        <v>4153.06</v>
+        <v>2699.79</v>
       </c>
       <c r="K40" t="n">
-        <v>20278.94</v>
+        <v>29883.37</v>
       </c>
       <c r="L40" t="n">
-        <v>20278.94</v>
+        <v>29883.37</v>
       </c>
       <c r="M40" t="n">
         <v>1.9</v>
       </c>
       <c r="N40" t="n">
-        <v>101801.0</v>
+        <v>101401.0</v>
       </c>
       <c r="O40" t="s">
         <v>66</v>
@@ -1103,46 +1142,46 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B41" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C41" t="n">
-        <v>1025.0</v>
+        <v>1012.0</v>
       </c>
       <c r="D41" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="E41" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F41" t="n">
         <v>1.0</v>
       </c>
       <c r="G41" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="H41" t="s">
         <v>81</v>
       </c>
       <c r="I41" t="n">
-        <v>7000.0</v>
+        <v>15000.0</v>
       </c>
       <c r="J41" t="n">
-        <v>820.28</v>
+        <v>360.92</v>
       </c>
       <c r="K41" t="n">
-        <v>6179.72</v>
+        <v>14639.08</v>
       </c>
       <c r="L41" t="n">
-        <v>6179.72</v>
+        <v>14639.08</v>
       </c>
       <c r="M41" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="N41" t="n">
-        <v>102501.0</v>
+        <v>101201.0</v>
       </c>
       <c r="O41" t="s">
         <v>81</v>
@@ -1156,115 +1195,350 @@
         <v>83</v>
       </c>
       <c r="C42" t="n">
-        <v>1024.0</v>
+        <v>1011.0</v>
       </c>
       <c r="D42" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="E42" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F42" t="n">
         <v>1.0</v>
       </c>
       <c r="G42" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="H42" t="s">
+        <v>84</v>
+      </c>
+      <c r="I42" t="n">
+        <v>60000.0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2201.56</v>
+      </c>
+      <c r="K42" t="n">
+        <v>57798.44</v>
+      </c>
+      <c r="L42" t="n">
+        <v>56160.77</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="N42" t="n">
+        <v>101101.0</v>
+      </c>
+      <c r="O42" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>85</v>
+      </c>
+      <c r="B43" t="s">
+        <v>53</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1017.0</v>
+      </c>
+      <c r="D43" t="s">
+        <v>79</v>
+      </c>
+      <c r="E43" t="s">
+        <v>55</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G43" t="s">
+        <v>86</v>
+      </c>
+      <c r="H43" t="s">
+        <v>87</v>
+      </c>
+      <c r="I43" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>101701.0</v>
+      </c>
+      <c r="O43" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>88</v>
+      </c>
+      <c r="B44" t="s">
+        <v>59</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1021.0</v>
+      </c>
+      <c r="D44" t="s">
+        <v>89</v>
+      </c>
+      <c r="E44" t="s">
+        <v>69</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G44" t="s">
+        <v>62</v>
+      </c>
+      <c r="H44" t="s">
+        <v>75</v>
+      </c>
+      <c r="I44" t="n">
+        <v>25000.0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>917.32</v>
+      </c>
+      <c r="K44" t="n">
+        <v>24082.68</v>
+      </c>
+      <c r="L44" t="n">
+        <v>24082.68</v>
+      </c>
+      <c r="M44" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N44" t="n">
+        <v>102101.0</v>
+      </c>
+      <c r="O44" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>90</v>
+      </c>
+      <c r="B45" t="s">
+        <v>91</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1018.0</v>
+      </c>
+      <c r="D45" t="s">
+        <v>89</v>
+      </c>
+      <c r="E45" t="s">
+        <v>92</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G45" t="s">
+        <v>62</v>
+      </c>
+      <c r="H45" t="s">
         <v>81</v>
       </c>
-      <c r="I42" t="n">
+      <c r="I45" t="n">
+        <v>24432.0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>4153.06</v>
+      </c>
+      <c r="K45" t="n">
+        <v>20278.94</v>
+      </c>
+      <c r="L45" t="n">
+        <v>20278.94</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="N45" t="n">
+        <v>101801.0</v>
+      </c>
+      <c r="O45" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>93</v>
+      </c>
+      <c r="B46" t="s">
+        <v>53</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1025.0</v>
+      </c>
+      <c r="D46" t="s">
+        <v>94</v>
+      </c>
+      <c r="E46" t="s">
+        <v>61</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G46" t="s">
+        <v>62</v>
+      </c>
+      <c r="H46" t="s">
+        <v>95</v>
+      </c>
+      <c r="I46" t="n">
+        <v>7000.0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>820.28</v>
+      </c>
+      <c r="K46" t="n">
+        <v>6179.72</v>
+      </c>
+      <c r="L46" t="n">
+        <v>6179.72</v>
+      </c>
+      <c r="M46" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="N46" t="n">
+        <v>102501.0</v>
+      </c>
+      <c r="O46" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>96</v>
+      </c>
+      <c r="B47" t="s">
+        <v>47</v>
+      </c>
+      <c r="C47" t="n">
+        <v>1024.0</v>
+      </c>
+      <c r="D47" t="s">
+        <v>94</v>
+      </c>
+      <c r="E47" t="s">
+        <v>49</v>
+      </c>
+      <c r="F47" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G47" t="s">
+        <v>62</v>
+      </c>
+      <c r="H47" t="s">
+        <v>95</v>
+      </c>
+      <c r="I47" t="n">
         <v>41000.0</v>
       </c>
-      <c r="J42" t="n">
+      <c r="J47" t="n">
         <v>1504.4</v>
       </c>
-      <c r="K42" t="n">
+      <c r="K47" t="n">
         <v>39495.6</v>
       </c>
-      <c r="L42" t="n">
+      <c r="L47" t="n">
         <v>39495.6</v>
       </c>
-      <c r="M42" t="n">
+      <c r="M47" t="n">
         <v>1.97</v>
       </c>
-      <c r="N42" t="n">
+      <c r="N47" t="n">
         <v>102401.0</v>
       </c>
-      <c r="O42" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>91</v>
+      <c r="O47" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>99</v>
+        <v>103</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/carteira_mensal/Set_2026.xlsx
+++ b/xlsx/carteira_mensal/Set_2026.xlsx
@@ -222,7 +222,7 @@
     <t>26/08/26</t>
   </si>
   <si>
-    <t>BIANCA RODRIGUES</t>
+    <t>bianca rodrigues</t>
   </si>
   <si>
     <t>VERA LUCIA NOGUEIRA FRANCO MOYSES</t>
